--- a/results/job_matches_2026-09-17.xlsx
+++ b/results/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>valency systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7faadf86698e0022</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II - Homes.com - Arlington, VA</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>valency systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
+          <t>https://www.indeed.com/viewjob?jk=7faadf86698e0022</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb6bc702cc8f819</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269ed9811c4ddaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cb40099cd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=269ed9811c4ddaf1</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8620f42415bd69</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cb40099cd54b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b47adc9fda6292</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8620f42415bd69</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - Python/JAVA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e860daaeaca47c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer III - Python/JAVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1559bf7f9b420</t>
+          <t>https://www.indeed.com/viewjob?jk=8e860daaeaca47c2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, BigQuery, Spark, PySpark, Kafka, Kafka Connect</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1559bf7f9b420</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Full Stack developer</t>
+          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, BigQuery, Spark, PySpark, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a16891b1a0bc2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Full Stack developer</t>
+          <t>Associate, AWS Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3cf1c715f20c75c</t>
+          <t>https://www.indeed.com/viewjob?jk=dceec67b928233eb</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a11df352ae6bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a16891b1a0bc2b6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Java Full Stack developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
+          <t>https://www.indeed.com/viewjob?jk=b3cf1c715f20c75c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Java Full Stack developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>National Computer Systems</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a11df352ae6bc1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid / Durham, NC</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186bcafa22d4b760</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfb266cf22e5317</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913f326777591b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ebbo</t>
+          <t>National Computer Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
+          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - GCP</t>
+          <t>Data Solutions Engineer - Hybrid / Durham, NC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Veson Nautical</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
+          <t>https://www.indeed.com/viewjob?jk=186bcafa22d4b760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Software Engineer 5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zencastr</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
+          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mpk Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
+          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
+          <t>https://www.indeed.com/viewjob?jk=913f326777591b8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>ebbo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
+          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Tech Consultant - Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83169a97751389a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Zencastr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41480985be8d777</t>
+          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technology - Enterprise Data Architect</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Mpk Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72f1d8c4f42885d</t>
+          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Automation QA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
+          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java API / Publication Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b6512cfed6eddc</t>
+          <t>https://www.indeed.com/viewjob?jk=a41480985be8d777</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aligned Data Centers</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Based in India</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credibly</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc86ee3cbc668eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nextech</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Melbourne, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,112 +1676,112 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
+          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Nextech</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Melbourne, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Aligned Data Centers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer-3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sinch</t>
+          <t>Hansei Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
+          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
+          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect, Enterprise Data Platform</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The J. M. Smucker Company</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orrville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables, Tableau</t>
+          <t>Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8264f5518d85c62b</t>
+          <t>https://www.indeed.com/viewjob?jk=adc10811ba8c4f6e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, MongoDB, Azure Cosmos DB, NoSQL, ETL, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ee9b464c973901</t>
+          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Identity Digital</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Polars, Snowflake, MLOps, MLflow, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
+          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Stardog Admin/DevOps Consultant</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, MongoDB, Azure Cosmos DB, NoSQL, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=45ee9b464c973901</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Stardog Admin</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
+          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Stardog Admin/DevOps Consultant</t>
+          <t>Data Architect, Enterprise Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>The J. M. Smucker Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Orrville, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
+          <t>https://www.indeed.com/viewjob?jk=8264f5518d85c62b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Ltd</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II - IT AI and Data Technology</t>
+          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>St. Peter's Health</t>
+          <t>Identity Digital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Databricks, GCP, BigQuery, Polars, Snowflake, MLOps, MLflow, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
+          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
+          <t>Stardog Admin</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - Ingestion Core team</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Alembic Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Data Engineer II - IT AI and Data Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>St. Peter's Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee14dc761cbf374d</t>
+          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Workday Financials Integration Developer (Consultant)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AG Consulting Partners</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
+          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer</t>
+          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Greenheck Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Schofield, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
+          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,29 +2621,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
+          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,147 +2656,147 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ee14dc761cbf374d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc8f98df2baf90f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - Enterprise Intelligence</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
+          <t>https://www.indeed.com/viewjob?jk=70cd80ce62300845</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer (Admin)</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a65a0fcd7eaa2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-3</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=814280d6c27316f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ef50bf754cb562dd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0632f545cc6501af</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56db417fdabcef</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8b20769edb6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf03e83c9963c7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Backend Java AWS Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a86278bda2e3b90</t>
+          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IS Data Architect</t>
+          <t>Senior Workday Financials Integration Developer (Consultant)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DBV Technologies</t>
+          <t>AG Consulting Partners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Data Modeling, ETL, ELT, Power BI, DataOps, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444fcfac41a73160</t>
+          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Corporate GenAI</t>
+          <t>DevOps &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Greenheck Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Schofield, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Calypso Java Developer Consultant</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tekserv</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Java and React Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,322 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76dab07201ea443a</t>
+          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Databricks Engineer (Admin)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Technical Business Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer-3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=814280d6c27316f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Java Application Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0632f545cc6501af</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71e8b20769edb6e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>IS Data Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>DBV Technologies</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Data Modeling, ETL, ELT, Power BI, DataOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=444fcfac41a73160</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Calypso Java Developer Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tekserv</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Corporate GenAI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AI Engineer, Industrial Systems Data Platform (ISDP)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbfa369c43ecbae0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-17.xlsx
+++ b/results/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Full Stack developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a11df352ae6bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfb266cf22e5317</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfb266cf22e5317</t>
+          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>National Computer Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
+          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Software Engineer 5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>National Computer Systems</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
+          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid / Durham, NC</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186bcafa22d4b760</t>
+          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer 5</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=913f326777591b8d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ebbo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913f326777591b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tech Consultant - Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ebbo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Zencastr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tech Consultant - Senior Full-Stack Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mpk Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
+          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zencastr</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mpk Solutions</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr. Sag Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>jobhuk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a6a52b4c199622</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a41480985be8d777</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41480985be8d777</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Aligned Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
+          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Nextech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Melbourne, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,77 +1711,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer-3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nextech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Melbourne, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aligned Data Centers</t>
+          <t>Hansei Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
+          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hansei Solutions</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
+          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sinch</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
+          <t>Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
+          <t>https://www.indeed.com/viewjob?jk=adc10811ba8c4f6e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
+          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adc10811ba8c4f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Data Architect, Enterprise Data Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>The J. M. Smucker Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orrville, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
+          <t>https://www.indeed.com/viewjob?jk=8264f5518d85c62b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, MongoDB, Azure Cosmos DB, NoSQL, ETL, Azure DevOps</t>
+          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ee9b464c973901</t>
+          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Identity Digital</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, BigQuery, Polars, Snowflake, MLOps, MLflow, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect, Enterprise Data Platform</t>
+          <t>Senior Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The J. M. Smucker Company</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Orrville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables, Tableau</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8264f5518d85c62b</t>
+          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
+          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
+          <t>Sr. Software Engineer - Ingestion Core team</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Identity Digital</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Polars, Snowflake, MLOps, MLflow, Kubernetes, Airflow</t>
+          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Stardog Admin/DevOps Consultant</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Alembic Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Stardog Admin</t>
+          <t>Data Engineer II - IT AI and Data Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>St. Peter's Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
+          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Ingestion Core team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Ltd</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II - IT AI and Data Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>St. Peter's Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
+          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
+          <t>https://www.indeed.com/viewjob?jk=333288494605fd23</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fd041e182434f1ce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
+          <t>https://www.indeed.com/viewjob?jk=fada807c5417b9e1</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Backend Java AWS Developer</t>
+          <t>DevOps &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Greenheck Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Schofield, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Workday Financials Integration Developer (Consultant)</t>
+          <t>Backend Java AWS Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AG Consulting Partners</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer</t>
+          <t>Senior Workday Financials Integration Developer (Consultant)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Greenheck Group</t>
+          <t>AG Consulting Partners</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Schofield, WI, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
+          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
+          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Engineer (Admin)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer (Admin)</t>
+          <t>Senior Technical Business Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Technical Business Analyst</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
+          <t>https://www.indeed.com/viewjob?jk=0632f545cc6501af</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-3</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=814280d6c27316f6</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8b20769edb6e4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Technica Corporation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0632f545cc6501af</t>
+          <t>https://www.indeed.com/viewjob?jk=9756d2f60173d6a6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Software Engineer - Corporate GenAI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8b20769edb6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IS Data Architect</t>
+          <t>Senior Calypso Java Developer Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DBV Technologies</t>
+          <t>Tekserv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Data Modeling, ETL, ELT, Power BI, DataOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444fcfac41a73160</t>
+          <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Calypso Java Developer Consultant</t>
+          <t>AI Engineer, Industrial Systems Data Platform (ISDP)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tekserv</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3295,76 +3295,6 @@
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Corporate GenAI</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>AI Engineer, Industrial Systems Data Platform (ISDP)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cbfa369c43ecbae0</t>
         </is>

--- a/results/job_matches_2026-09-17.xlsx
+++ b/results/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI and Data Solution Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=95fd25995bfa0bb4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI and Data Solution Architect</t>
+          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>A/AI Machine Learning Engineering Stf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>valency systems</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7faadf86698e0022</t>
+          <t>https://www.indeed.com/viewjob?jk=601d6d86d645df17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=6bab71f3dab957b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer II - Homes.com - Arlington, VA</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Talend</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269ed9811c4ddaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>valency systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cb40099cd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=7faadf86698e0022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8620f42415bd69</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - Python/JAVA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e860daaeaca47c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer III - Python/JAVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1559bf7f9b420</t>
+          <t>https://www.indeed.com/viewjob?jk=8e860daaeaca47c2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, BigQuery, Spark, PySpark, Kafka, Kafka Connect</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1559bf7f9b420</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate, AWS Data Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dceec67b928233eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d445976e1497f7fc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Full Stack developer</t>
+          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, BigQuery, Spark, PySpark, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a16891b1a0bc2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Full Stack developer</t>
+          <t>Associate, AWS Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3cf1c715f20c75c</t>
+          <t>https://www.indeed.com/viewjob?jk=dceec67b928233eb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Java Developer with Python</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfb266cf22e5317</t>
+          <t>https://www.indeed.com/viewjob?jk=406ebbb1091929da</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Java Developer with Python &amp; DB2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
+          <t>https://www.indeed.com/viewjob?jk=94bc62a1961aa054</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>National Computer Systems</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,234 +1091,234 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfb266cf22e5317</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 5</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Java - Python Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ef0ed669955b387</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913f326777591b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=13dc5ea105826d16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ebbo</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
+          <t>https://www.indeed.com/viewjob?jk=978f9a7dd296c785</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
+          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tech Consultant - Senior Full-Stack Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
+          <t>https://www.indeed.com/viewjob?jk=73f7f04e13cfaaec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zencastr</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
+          <t>https://www.indeed.com/viewjob?jk=48f9cd78305a0219</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mpk Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
+          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Tech Consultant - Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
+          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>Zencastr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Sag Architect</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jobhuk</t>
+          <t>Mpk Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a6a52b4c199622</t>
+          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Azure Data Engineer at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41480985be8d777</t>
+          <t>https://www.indeed.com/viewjob?jk=22df130d2e5b276e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
+          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,137 +1651,137 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
+          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Architect - Azure Data &amp; AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aligned Data Centers</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Kafka, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nextech</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Melbourne, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hansei Solutions</t>
+          <t>Aligned Data Centers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
+          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Nextech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Melbourne, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer-3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Hansei Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sinch</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
+          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adc10811ba8c4f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=adc10811ba8c4f6e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
+          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect, Enterprise Data Platform</t>
+          <t>Sr. Software Engineer - Ingestion Core team</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The J. M. Smucker Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orrville, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables, Tableau</t>
+          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8264f5518d85c62b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Alembic Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
+          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
+          <t>Data Engineer II - IT AI and Data Technology</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Identity Digital</t>
+          <t>St. Peter's Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Polars, Snowflake, MLOps, MLflow, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
+          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Stardog Admin/DevOps Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
+          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Ingestion Core team</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29ca22c38298f5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Ltd</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=333288494605fd23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II - IT AI and Data Technology</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>St. Peter's Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
+          <t>https://www.indeed.com/viewjob?jk=fd041e182434f1ce</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
+          <t>https://www.indeed.com/viewjob?jk=fada807c5417b9e1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff62d532162ce32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Greenheck Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Schofield, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
+          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Backend Java AWS Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333288494605fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Workday Financials Integration Developer (Consultant)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>AG Consulting Partners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd041e182434f1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Automation Engineer (UI/API)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fada807c5417b9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc8f98df2baf90f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee14dc761cbf374d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe0246c0ac0ed63f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Institutional Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of South Carolina</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Richland, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc8f98df2baf90f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad752dd5b859ec10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Senior Databricks Engineer (Admin)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cd80ce62300845</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a65a0fcd7eaa2</t>
+          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Senior Technical Business Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,497 +2806,77 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef50bf754cb562dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Senior Software Engineer - Corporate GenAI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56db417fdabcef</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Senior Calypso Java Developer Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tekserv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf03e83c9963c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Security Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Greenheck Group</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Schofield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Backend Java AWS Developer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>All IT Solutions</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Workday Financials Integration Developer (Consultant)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>AG Consulting Partners</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Olympia, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Syngenta</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Databricks Engineer (Admin)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Technical Business Analyst</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Java Application Architect</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0632f545cc6501af</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8b20769edb6e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Full-Stack Java Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Technica Corporation</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9756d2f60173d6a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Corporate GenAI</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Calypso Java Developer Consultant</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tekserv</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI Engineer, Industrial Systems Data Platform (ISDP)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfa369c43ecbae0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-17.xlsx
+++ b/results/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Application Integration Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, IAM, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,94 +496,94 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fd25995bfa0bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae081f8bfbda2059</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
+          <t>https://www.indeed.com/viewjob?jk=95fd25995bfa0bb4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A/AI Machine Learning Engineering Stf</t>
+          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601d6d86d645df17</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Snowflake Platform Admin + Data Engineer</t>
+          <t>A/AI Machine Learning Engineering Stf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bab71f3dab957b3</t>
+          <t>https://www.indeed.com/viewjob?jk=601d6d86d645df17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI and Data Solution Architect</t>
+          <t>Senior Data Engineer Con II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4db0b036f71a516</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI and Data Solution Architect</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=6bab71f3dab957b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>valency systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7faadf86698e0022</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II - Homes.com - Arlington, VA</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
+          <t>https://www.indeed.com/viewjob?jk=228fcb0437db4c81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - Python/JAVA</t>
+          <t>Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e860daaeaca47c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
         </is>
       </c>
     </row>
@@ -858,20 +858,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling</t>
+          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1559bf7f9b420</t>
+          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ECPI University</t>
+          <t>CodeCombat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13dc5ea105826d16</t>
+          <t>https://www.indeed.com/viewjob?jk=96af3bdac24317bb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978f9a7dd296c785</t>
+          <t>https://www.indeed.com/viewjob?jk=13dc5ea105826d16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer 5</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=978f9a7dd296c785</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Architect – FDE | Hartford, CT / Minneapolis, MN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inabia Software &amp; Consulting Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f7f04e13cfaaec</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b512ada906a24d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Developer (Two Vacancies)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ECPI University</t>
+          <t>Smithsonian Enterprises</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f9cd78305a0219</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9260fd2e400292</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Software Engineer 5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
+          <t>https://www.indeed.com/viewjob?jk=73f7f04e13cfaaec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tech Consultant - Senior Full-Stack Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
+          <t>https://www.indeed.com/viewjob?jk=48f9cd78305a0219</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zencastr</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Dataflow, Spark, Scala, Snowflake, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc787126ad9474ae</t>
+          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Tech Consultant - Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mpk Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f94a146708ee43</t>
+          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer at Major Japanese Bank</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22df130d2e5b276e</t>
+          <t>https://www.indeed.com/viewjob?jk=4318b5d5a1fa8d7b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d01e92d858fdabd9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Intern, Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Pediatric Associates Family of Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,29 +1606,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
+          <t>https://www.indeed.com/viewjob?jk=5e78dfc216dc63c0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
+          <t>Azure Data Engineer at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
+          <t>https://www.indeed.com/viewjob?jk=22df130d2e5b276e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Architect - Azure Data &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Kafka, ETL, ELT, Power BI</t>
+          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
+          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aligned Data Centers</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Architect - Azure Data &amp; AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nextech</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Melbourne, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Kafka, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
+          <t>https://www.indeed.com/viewjob?jk=965af74ac3a4f28b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hansei Solutions</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
+          <t>https://www.indeed.com/viewjob?jk=84b8ba5b4701ac07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,164 +1931,164 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>ICBD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0d34c2d7c8f353</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Automation &amp; Observability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f68ad5e40f728b9f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Mid Astro Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adc10811ba8c4f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa7964c7f50144e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Mid Astro Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fa68d04c53f7305c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
+          <t>https://www.indeed.com/viewjob?jk=3dbcf1eaec6697a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer-3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Ingestion Core team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hansei Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Scala, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0200e366b920258d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Ltd</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer II - IT AI and Data Technology</t>
+          <t>4572 Software Development Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>St. Peter's Health</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbd91cc3292ce05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Dask, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
+          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Software Engineering and Cloud Platforms, Early Career</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a6ea7b7776e3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fff9ab8e0bdf65bf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Sr. Software Engineer - Ingestion Core team</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Azure DevOps</t>
+          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29ca22c38298f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Alembic Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333288494605fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer II - IT AI and Data Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>St. Peter's Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd041e182434f1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fada807c5417b9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29ca22c38298f5</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Workday Financials Integration Developer (Consultant)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AG Consulting Partners</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, DynamoDB, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
+          <t>https://www.indeed.com/viewjob?jk=2830b10b4939c5e0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Software Engineer, DNS &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc8f98df2baf90f</t>
+          <t>https://www.indeed.com/viewjob?jk=998b59d45987a604</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Associate AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d761a996e119319</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Technical Business Analyst</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa577a3ce581c79</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Corporate GenAI</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Calypso Java Developer Consultant</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tekserv</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,17 +2866,122 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f81d7b9839378748</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Technical Business Analyst</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer 2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Splunk, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd4b4423de389261</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Engineer III, Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Mobis Parts America, LLC.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fountain Valley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6448e49f67d965f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-17.xlsx
+++ b/results/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Hospice of the Valley (AZ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,89 +531,89 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fd25995bfa0bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7337bb4d468da95</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
+          <t>https://www.indeed.com/viewjob?jk=95fd25995bfa0bb4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A/AI Machine Learning Engineering Stf</t>
+          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601d6d86d645df17</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Con II</t>
+          <t>A/AI Machine Learning Engineering Stf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4db0b036f71a516</t>
+          <t>https://www.indeed.com/viewjob?jk=601d6d86d645df17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Platform Admin + Data Engineer</t>
+          <t>Senior Data Engineer Con II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bab71f3dab957b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4db0b036f71a516</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI and Data Solution Architect</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=6bab71f3dab957b3</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=228fcb0437db4c81</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II - Homes.com - Arlington, VA</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
+          <t>https://www.indeed.com/viewjob?jk=228fcb0437db4c81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Architect, Cloud &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d445976e1497f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4dc9c1e83b836220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, BigQuery, Spark, PySpark, Kafka, Kafka Connect</t>
+          <t>BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=68a757252287b525</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate, AWS Data Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dceec67b928233eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d445976e1497f7fc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Developer with Python</t>
+          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, BigQuery, Spark, PySpark, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406ebbb1091929da</t>
+          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Developer with Python &amp; DB2</t>
+          <t>Associate, AWS Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bc62a1961aa054</t>
+          <t>https://www.indeed.com/viewjob?jk=dceec67b928233eb</t>
         </is>
       </c>
     </row>
@@ -1098,60 +1098,60 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior AWS Full Stack Engineer local only</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>VaaridaTech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, S3, SQS, Azure, Scala, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, IAM, Azure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8284bacdead0a51</t>
+          <t>https://www.indeed.com/viewjob?jk=99e004b7468d7a58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java - Python Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CodeCombat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ef0ed669955b387</t>
+          <t>https://www.indeed.com/viewjob?jk=96af3bdac24317bb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Contact Center Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CodeCombat</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96af3bdac24317bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9a0e1dc867d738</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 5</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=73f7f04e13cfaaec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Software Engineer 5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f7f04e13cfaaec</t>
+          <t>https://www.indeed.com/viewjob?jk=20a24396a4d385dc</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tech Consultant - Senior Full-Stack Engineer</t>
+          <t>Software Development - Analyst II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CTIS, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,139 +1501,139 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, REST API integration</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7f9a1049d0daf8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, S3, ECS, IAM, Azure, Scala, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4318b5d5a1fa8d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=73ee8bf798535ec7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mid Software Engineer</t>
+          <t>Sr. Blue Blue Yonder WMS Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Numen International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Wisconsin Rapids, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01e92d858fdabd9</t>
+          <t>https://www.indeed.com/viewjob?jk=df54cb763cc8f35e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Intern, Data Engineering</t>
+          <t>Tech Consultant - Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pediatric Associates Family of Companies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e78dfc216dc63c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Data Engineer at Major Japanese Bank</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22df130d2e5b276e</t>
+          <t>https://www.indeed.com/viewjob?jk=4318b5d5a1fa8d7b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d01e92d858fdabd9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Azure Data Engineer at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,29 +1711,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
+          <t>https://www.indeed.com/viewjob?jk=22df130d2e5b276e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Oracle, Spark &amp; Cloud Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>IAM, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744f32dc4d7988bb</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed7d1d06626f3f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Vertex AI, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Architect - Azure Data &amp; AI</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Kafka, ETL, ELT, Power BI</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, Oozie, Flume, YARN, Impala, Spark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbd05e0ada74799</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Architect - Azure Data &amp; AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Kafka, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965af74ac3a4f28b</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b8ba5b4701ac07</t>
+          <t>https://www.indeed.com/viewjob?jk=965af74ac3a4f28b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
+          <t>https://www.indeed.com/viewjob?jk=84b8ba5b4701ac07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICBD</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0d34c2d7c8f353</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Automation &amp; Observability Engineer</t>
+          <t>DevOps Engineer - Technology Solutions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>University of Illinois</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68ad5e40f728b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4449e01c5ed9ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mid Astro Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>ICBD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa7964c7f50144e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0d34c2d7c8f353</t>
         </is>
       </c>
     </row>
@@ -2066,64 +2066,64 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa68d04c53f7305c</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa7964c7f50144e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Mid Astro Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dbcf1eaec6697a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fa68d04c53f7305c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2345bd6032d37d</t>
+          <t>https://www.indeed.com/viewjob?jk=3dbcf1eaec6697a7</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cc8e84664627f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4572 Software Development Engineer III</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbd91cc3292ce05</t>
+          <t>https://www.indeed.com/viewjob?jk=27203176a444972f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>4572 Software Development Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbd91cc3292ce05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff9ab8e0bdf65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Ingestion Core team</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fff9ab8e0bdf65bf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Software Engineer - Ingestion Core team</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Ltd</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>SQS, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7552bca788f2c3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II - IT AI and Data Technology</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>St. Peter's Health</t>
+          <t>Alembic Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Spark, Scala, Kafka, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24058fb3749fead</t>
+          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Cloud Systems Architect (226 Days)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Dallas Independent School District</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29ca22c38298f5</t>
+          <t>https://www.indeed.com/viewjob?jk=866755e4f8ce63a3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Developer - Analytics Engineer Department of Pharmacy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Duke Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps</t>
+          <t>RDS, Azure, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff62d532162ce32</t>
+          <t>https://www.indeed.com/viewjob?jk=96982bb63995138d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer</t>
+          <t>Senior Software Engineer - OMS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Greenheck Group</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Schofield, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e54cf349fa6158e</t>
+          <t>https://www.indeed.com/viewjob?jk=07ed335054406c39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Java AWS Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Data Modeling, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=29ef6391ee65877b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Backend Java AWS Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>All IT Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, DynamoDB, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Glue, EMR, S3, Spark, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2830b10b4939c5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf369a38badd5d9f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer, DNS &amp; Cloud Infrastructure</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Aceable</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998b59d45987a604</t>
+          <t>https://www.indeed.com/viewjob?jk=946f9885537eb383</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, DNS &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe0246c0ac0ed63f</t>
+          <t>https://www.indeed.com/viewjob?jk=998b59d45987a604</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer (Admin)</t>
+          <t>Associate AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fa128ecb47403c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d761a996e119319</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate AWS DevOps Engineer</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d761a996e119319</t>
+          <t>https://www.indeed.com/viewjob?jk=91283bd30c9609b4</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior DevOpsSRE Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f44421eecd0c683</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VoltaGrid</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, Lambda, S3, SQS, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81d7b9839378748</t>
+          <t>https://www.indeed.com/viewjob?jk=24b02a3e8026450a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Technical Business Analyst</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
+          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Technical Business Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Splunk, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4b4423de389261</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer III, Business Intelligence</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,50 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Splunk, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd4b4423de389261</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Engineer III, Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Mobis Parts America, LLC.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fountain Valley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f6448e49f67d965f</t>
         </is>
